--- a/apps/teammatcher/teammates.xlsx
+++ b/apps/teammatcher/teammates.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yslee/git/samse.github.io/apps/teammatcher/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yslee/git/teammatcher/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F01DA9D-6973-E641-B619-85EFDD3DAEBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AA88CC-8E44-4F41-BF21-916A7E78FABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10360" yWindow="660" windowWidth="11660" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -255,23 +255,20 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>성별</t>
+  </si>
+  <si>
     <t>남</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>여</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>성별</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -285,6 +282,13 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -307,8 +311,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -655,8 +660,8 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>66</v>
+      <c r="B1" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -672,8 +677,8 @@
       <c r="A2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
-        <v>64</v>
+      <c r="B2" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -689,8 +694,8 @@
       <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
-        <v>64</v>
+      <c r="B3" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C3">
         <v>-1</v>
@@ -706,8 +711,8 @@
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
-        <v>64</v>
+      <c r="B4" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C4">
         <v>-6</v>
@@ -723,8 +728,8 @@
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
-        <v>65</v>
+      <c r="B5" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C5">
         <v>-2</v>
@@ -740,8 +745,8 @@
       <c r="A6" t="s">
         <v>52</v>
       </c>
-      <c r="B6" t="s">
-        <v>65</v>
+      <c r="B6" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -754,8 +759,8 @@
       <c r="A7" t="s">
         <v>59</v>
       </c>
-      <c r="B7" t="s">
-        <v>64</v>
+      <c r="B7" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -768,8 +773,8 @@
       <c r="A8" t="s">
         <v>49</v>
       </c>
-      <c r="B8" t="s">
-        <v>65</v>
+      <c r="B8" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C8">
         <v>2.4</v>
@@ -782,8 +787,8 @@
       <c r="A9" t="s">
         <v>55</v>
       </c>
-      <c r="B9" t="s">
-        <v>64</v>
+      <c r="B9" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -796,8 +801,8 @@
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
-        <v>64</v>
+      <c r="B10" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C10">
         <v>6</v>
@@ -813,8 +818,8 @@
       <c r="A11" t="s">
         <v>50</v>
       </c>
-      <c r="B11" t="s">
-        <v>65</v>
+      <c r="B11" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C11">
         <v>23</v>
@@ -827,8 +832,8 @@
       <c r="A12" t="s">
         <v>45</v>
       </c>
-      <c r="B12" t="s">
-        <v>65</v>
+      <c r="B12" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -841,8 +846,8 @@
       <c r="A13" t="s">
         <v>46</v>
       </c>
-      <c r="B13" t="s">
-        <v>65</v>
+      <c r="B13" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C13">
         <v>-3</v>
@@ -855,8 +860,8 @@
       <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B14" t="s">
-        <v>65</v>
+      <c r="B14" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -872,8 +877,8 @@
       <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="B15" t="s">
-        <v>65</v>
+      <c r="B15" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -889,8 +894,8 @@
       <c r="A16" t="s">
         <v>44</v>
       </c>
-      <c r="B16" t="s">
-        <v>64</v>
+      <c r="B16" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -906,8 +911,8 @@
       <c r="A17" t="s">
         <v>63</v>
       </c>
-      <c r="B17" t="s">
-        <v>64</v>
+      <c r="B17" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C17">
         <v>-4</v>
@@ -923,8 +928,8 @@
       <c r="A18" t="s">
         <v>14</v>
       </c>
-      <c r="B18" t="s">
-        <v>65</v>
+      <c r="B18" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C18">
         <v>10.199999999999999</v>
@@ -940,8 +945,8 @@
       <c r="A19" t="s">
         <v>15</v>
       </c>
-      <c r="B19" t="s">
-        <v>64</v>
+      <c r="B19" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C19">
         <v>-8</v>
@@ -957,8 +962,8 @@
       <c r="A20" t="s">
         <v>16</v>
       </c>
-      <c r="B20" t="s">
-        <v>64</v>
+      <c r="B20" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C20">
         <v>-10</v>
@@ -974,8 +979,8 @@
       <c r="A21" t="s">
         <v>17</v>
       </c>
-      <c r="B21" t="s">
-        <v>65</v>
+      <c r="B21" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -991,8 +996,8 @@
       <c r="A22" t="s">
         <v>18</v>
       </c>
-      <c r="B22" t="s">
-        <v>65</v>
+      <c r="B22" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C22">
         <v>15.2</v>
@@ -1008,8 +1013,8 @@
       <c r="A23" t="s">
         <v>20</v>
       </c>
-      <c r="B23" t="s">
-        <v>64</v>
+      <c r="B23" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C23">
         <v>1.5</v>
@@ -1025,8 +1030,8 @@
       <c r="A24" t="s">
         <v>21</v>
       </c>
-      <c r="B24" t="s">
-        <v>64</v>
+      <c r="B24" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C24">
         <v>-5.2</v>
@@ -1042,8 +1047,8 @@
       <c r="A25" t="s">
         <v>22</v>
       </c>
-      <c r="B25" t="s">
-        <v>64</v>
+      <c r="B25" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C25">
         <v>-2.2000000000000002</v>
@@ -1059,8 +1064,8 @@
       <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B26" t="s">
-        <v>64</v>
+      <c r="B26" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -1073,8 +1078,8 @@
       <c r="A27" t="s">
         <v>19</v>
       </c>
-      <c r="B27" t="s">
-        <v>64</v>
+      <c r="B27" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C27">
         <v>15</v>
@@ -1090,8 +1095,8 @@
       <c r="A28" t="s">
         <v>58</v>
       </c>
-      <c r="B28" t="s">
-        <v>65</v>
+      <c r="B28" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C28">
         <v>4.2</v>
@@ -1104,8 +1109,8 @@
       <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
-        <v>64</v>
+      <c r="B29" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -1118,8 +1123,8 @@
       <c r="A30" t="s">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>64</v>
+      <c r="B30" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C30">
         <v>7</v>
@@ -1132,8 +1137,8 @@
       <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>64</v>
+      <c r="B31" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -1146,8 +1151,8 @@
       <c r="A32" t="s">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>64</v>
+      <c r="B32" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C32">
         <v>5</v>
@@ -1160,8 +1165,8 @@
       <c r="A33" t="s">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
-        <v>64</v>
+      <c r="B33" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C33">
         <v>3</v>
@@ -1174,8 +1179,8 @@
       <c r="A34" t="s">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>64</v>
+      <c r="B34" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -1188,8 +1193,8 @@
       <c r="A35" t="s">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
-        <v>64</v>
+      <c r="B35" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C35">
         <v>5</v>
@@ -1202,8 +1207,8 @@
       <c r="A36" t="s">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>64</v>
+      <c r="B36" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C36">
         <v>3</v>
@@ -1216,8 +1221,8 @@
       <c r="A37" t="s">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
-        <v>65</v>
+      <c r="B37" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C37">
         <v>5</v>
@@ -1230,8 +1235,8 @@
       <c r="A38" t="s">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
-        <v>64</v>
+      <c r="B38" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C38">
         <v>3</v>
@@ -1244,8 +1249,8 @@
       <c r="A39" t="s">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
-        <v>64</v>
+      <c r="B39" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C39">
         <v>-5</v>
@@ -1258,8 +1263,8 @@
       <c r="A40" t="s">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>65</v>
+      <c r="B40" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C40">
         <v>10</v>
@@ -1272,8 +1277,8 @@
       <c r="A41" t="s">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
-        <v>65</v>
+      <c r="B41" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C41">
         <v>16</v>
@@ -1286,8 +1291,8 @@
       <c r="A42" t="s">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
-        <v>64</v>
+      <c r="B42" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -1300,8 +1305,8 @@
       <c r="A43" t="s">
         <v>42</v>
       </c>
-      <c r="B43" t="s">
-        <v>65</v>
+      <c r="B43" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C43">
         <v>4</v>
@@ -1314,8 +1319,8 @@
       <c r="A44" t="s">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
-        <v>65</v>
+      <c r="B44" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C44">
         <v>11</v>
@@ -1328,8 +1333,8 @@
       <c r="A45" t="s">
         <v>47</v>
       </c>
-      <c r="B45" t="s">
-        <v>65</v>
+      <c r="B45" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C45">
         <v>10</v>
@@ -1342,8 +1347,8 @@
       <c r="A46" t="s">
         <v>48</v>
       </c>
-      <c r="B46" t="s">
-        <v>64</v>
+      <c r="B46" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -1356,8 +1361,8 @@
       <c r="A47" t="s">
         <v>51</v>
       </c>
-      <c r="B47" t="s">
-        <v>65</v>
+      <c r="B47" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C47">
         <v>5</v>
@@ -1370,8 +1375,8 @@
       <c r="A48" t="s">
         <v>53</v>
       </c>
-      <c r="B48" t="s">
-        <v>65</v>
+      <c r="B48" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C48">
         <v>10</v>
@@ -1384,8 +1389,8 @@
       <c r="A49" t="s">
         <v>54</v>
       </c>
-      <c r="B49" t="s">
-        <v>64</v>
+      <c r="B49" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C49">
         <v>-4</v>
@@ -1398,8 +1403,8 @@
       <c r="A50" t="s">
         <v>56</v>
       </c>
-      <c r="B50" t="s">
-        <v>64</v>
+      <c r="B50" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C50">
         <v>3</v>
@@ -1412,8 +1417,8 @@
       <c r="A51" t="s">
         <v>57</v>
       </c>
-      <c r="B51" t="s">
-        <v>64</v>
+      <c r="B51" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -1426,8 +1431,8 @@
       <c r="A52" t="s">
         <v>60</v>
       </c>
-      <c r="B52" t="s">
-        <v>65</v>
+      <c r="B52" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C52">
         <v>10</v>
@@ -1440,8 +1445,8 @@
       <c r="A53" t="s">
         <v>61</v>
       </c>
-      <c r="B53" t="s">
-        <v>65</v>
+      <c r="B53" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C53">
         <v>11</v>

--- a/apps/teammatcher/teammates.xlsx
+++ b/apps/teammatcher/teammates.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yslee/git/teammatcher/public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yslee/git/samse.github.io/apps/teammatcher/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AA88CC-8E44-4F41-BF21-916A7E78FABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C060D5C-D8F1-5E4E-B49F-632BBC86F727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10360" yWindow="660" windowWidth="11660" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="63">
   <si>
     <t>별명</t>
   </si>
@@ -46,12 +46,6 @@
     <t>천사</t>
   </si>
   <si>
-    <t>골프새</t>
-  </si>
-  <si>
-    <t>느림</t>
-  </si>
-  <si>
     <t>초이정</t>
   </si>
   <si>
@@ -123,18 +117,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>독고탁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>롱기스강</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>루시하부자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>루카스</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -231,10 +217,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>초이정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>캡틴정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -262,6 +244,10 @@
   </si>
   <si>
     <t>여</t>
+  </si>
+  <si>
+    <t>동그리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -653,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -661,7 +647,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -675,33 +661,33 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C3">
         <v>-1</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -712,7 +698,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C4">
         <v>-6</v>
@@ -729,7 +715,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C5">
         <v>-2</v>
@@ -743,117 +729,117 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C8">
         <v>2.4</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C10">
-        <v>6</v>
-      </c>
-      <c r="D10" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C11">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C13">
-        <v>-3</v>
+        <v>2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -861,95 +847,95 @@
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C17">
-        <v>-4</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C18">
-        <v>10.199999999999999</v>
+        <v>-8</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C19">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
@@ -960,13 +946,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C20">
-        <v>-10</v>
+        <v>4</v>
       </c>
       <c r="D20" t="s">
         <v>5</v>
@@ -977,13 +963,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>15.2</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
@@ -997,378 +983,375 @@
         <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C22">
-        <v>15.2</v>
+        <v>1.5</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C23">
-        <v>1.5</v>
+        <v>-5.2</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C24">
-        <v>-5.2</v>
+        <v>-2.2000000000000002</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C25">
-        <v>-2.2000000000000002</v>
-      </c>
-      <c r="D25" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>15</v>
+      </c>
+      <c r="D26" t="s">
+        <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C27">
-        <v>15</v>
-      </c>
-      <c r="D27" t="s">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="E27" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C28">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C32">
         <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C33">
         <v>3</v>
       </c>
       <c r="E33" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E34" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C35">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E35" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="E36" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C39">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="E39" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C40">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E40" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C41">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E41" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E42" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C44">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E44" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C45">
         <v>10</v>
       </c>
       <c r="E45" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="E46" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E47" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1376,27 +1359,27 @@
         <v>53</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C48">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C49">
-        <v>-4</v>
+        <v>10</v>
       </c>
       <c r="E49" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1404,62 +1387,20 @@
         <v>56</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C50">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E50" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-      <c r="E51" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" t="s">
-        <v>60</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C52">
-        <v>10</v>
-      </c>
-      <c r="E52" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" t="s">
-        <v>61</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C53">
-        <v>11</v>
-      </c>
-      <c r="E53" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C14:E15 C1:E1 D16:E16 C24:D25 C4:E5 C10:E10 C17:E23 A10 A4:A5 A18:A25 A1 A14:A15" numberStoredAsText="1"/>
+    <ignoredError sqref="C13:E14 C1:E1 D15:E15 C23:D24 C4:E5 C16:E22 A4:A5 A17:A24 A1 A13:A14" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/apps/teammatcher/teammates.xlsx
+++ b/apps/teammatcher/teammates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yslee/git/samse.github.io/apps/teammatcher/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C060D5C-D8F1-5E4E-B49F-632BBC86F727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D52E4C-7CA5-4442-BFE7-64309D50EC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10360" yWindow="660" windowWidth="11660" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="62">
   <si>
     <t>별명</t>
   </si>
@@ -89,14 +89,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이요삼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김시년</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>알랑가모르간</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -247,6 +239,10 @@
   </si>
   <si>
     <t>동그리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>느림</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -647,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -664,16 +660,13 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -681,13 +674,10 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C3">
         <v>-1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -698,7 +688,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C4">
         <v>-6</v>
@@ -715,7 +705,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C5">
         <v>-2</v>
@@ -729,100 +719,100 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C8">
         <v>2.4</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C10">
         <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C11">
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C12">
         <v>-3</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -830,7 +820,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -847,7 +837,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -861,10 +851,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -878,10 +868,10 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C16">
         <v>-4</v>
@@ -898,7 +888,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C17">
         <v>10.199999999999999</v>
@@ -915,7 +905,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C18">
         <v>-8</v>
@@ -932,7 +922,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C19">
         <v>-10</v>
@@ -949,7 +939,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C20">
         <v>4</v>
@@ -966,7 +956,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C21">
         <v>15.2</v>
@@ -983,7 +973,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C22">
         <v>1.5</v>
@@ -1000,7 +990,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C23">
         <v>-5.2</v>
@@ -1009,7 +999,7 @@
         <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1017,7 +1007,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C24">
         <v>-2.2000000000000002</v>
@@ -1026,21 +1016,21 @@
         <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1048,7 +1038,7 @@
         <v>17</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C26">
         <v>15</v>
@@ -1062,338 +1052,338 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C27">
         <v>-2</v>
       </c>
       <c r="E27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C29">
         <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
       <c r="E30" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C31">
         <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C32">
         <v>5</v>
       </c>
       <c r="E32" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C33">
         <v>3</v>
       </c>
       <c r="E33" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C34">
         <v>5</v>
       </c>
       <c r="E34" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C35">
         <v>3</v>
       </c>
       <c r="E35" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <v>-5</v>
       </c>
       <c r="E36" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C37">
         <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C38">
         <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C39">
         <v>2</v>
       </c>
       <c r="E39" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C40">
         <v>4</v>
       </c>
       <c r="E40" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C41">
         <v>11</v>
       </c>
       <c r="E41" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C42">
         <v>10</v>
       </c>
       <c r="E42" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C44">
         <v>5</v>
       </c>
       <c r="E44" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C45">
         <v>10</v>
       </c>
       <c r="E45" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C46">
         <v>-4</v>
       </c>
       <c r="E46" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C47">
         <v>3</v>
       </c>
       <c r="E47" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C49">
         <v>10</v>
       </c>
       <c r="E49" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C50">
         <v>11</v>
       </c>
       <c r="E50" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
